--- a/news_daily/2026-08-26.xlsx
+++ b/news_daily/2026-08-26.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BL12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,6 +534,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,6 +839,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -1007,6 +1031,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1057,13 +1085,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1108,7 +1140,11 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>e546a631c77e4fa8bc8a4cc27a6724fb</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>fdde003085f4c9c55c521d98</t>
@@ -1129,7 +1165,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -1173,6 +1213,18 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1223,13 +1275,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1278,7 +1334,11 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>6e6e27fa253d47d58879905fb3efd898</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>64533d28a77ef9a251dd91c9</t>
@@ -1299,7 +1359,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -1343,6 +1407,18 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1505,6 +1581,10 @@
         </is>
       </c>
       <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr"/>
+      <c r="BL5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1555,13 +1635,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1606,7 +1690,11 @@
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>43cedf0db261483aa353f50bb7820965</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>5e643003c46200dc2257791e</t>
@@ -1627,7 +1715,11 @@
       <c r="AL6" s="3" t="inlineStr"/>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="3" t="inlineStr"/>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
@@ -1671,6 +1763,18 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1841,6 +1945,10 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1891,13 +1999,17 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -1946,7 +2058,11 @@
         </is>
       </c>
       <c r="AA8" s="5" t="inlineStr"/>
-      <c r="AB8" s="5" t="inlineStr"/>
+      <c r="AB8" s="5" t="inlineStr">
+        <is>
+          <t>89b8cdd9449f41fba33e7fcb2fab5ff6</t>
+        </is>
+      </c>
       <c r="AC8" s="5" t="inlineStr">
         <is>
           <t>6f7308482508a9851ede7f08</t>
@@ -1967,7 +2083,11 @@
       <c r="AL8" s="5" t="inlineStr"/>
       <c r="AM8" s="5" t="inlineStr"/>
       <c r="AN8" s="5" t="inlineStr"/>
-      <c r="AO8" s="5" t="inlineStr"/>
+      <c r="AO8" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="5" t="inlineStr"/>
       <c r="AQ8" s="5" t="inlineStr"/>
       <c r="AR8" s="5" t="inlineStr"/>
@@ -2011,168 +2131,208 @@
         </is>
       </c>
       <c r="BH8" s="5" t="inlineStr"/>
+      <c r="BI8" s="5" t="inlineStr"/>
+      <c r="BJ8" s="5" t="inlineStr"/>
+      <c r="BK8" s="5" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>APO</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Apollo Global Management</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>2026-08-26T13:23:59+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>The Bull Case For Apollo Global Management (APO) Could Change Following Cybersecurity Breach And Legal Settlement News - Learn Why</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>資料外洩</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>'-0.637</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOVFk1TmwtTk5nSGlObGczd2tKb3JxZ19QMHF3TjY0dnpsX3dGVTNxcUViLVhCcmZHZFVSZEFtNzhwUmtPb1Q2bUNGSi1MQmduT3ZDM3FCbmNCMHBMQnBPbnlHZFBxTk5OclJCTm5tZDdVOTdlYUlpTEZFb0REc0Q1NlA3Qmw3V0ludFFqakVJSzlhOUNxbXRRSnhQUFlRcG16SGFUZ0hOcUhQS3Byb3RpbGdoQzJRdXJtYTkxcVVkREx4WldpdG5zOHVRbWVOLXBVak9Va3JMNk1vWXhCSGdLelFrNmMtZ3gxd3dr0gHwAUFVX3lxTE5Bc2F6dVA4TlhXbm01RWRzZkFqM3RTT3pDWFlOOHBLMVA3MG1mNW8xek9sOXFvR09yZnk4VldzU1ZXS052NEV1T18yaXZLUXJzNHo0SzVERHdCdTd4U1VQQ216RHRLcldGZzlQMDhVbTFKeFRfMTdnU3g0UXAtMXNMQllRN0R4VE5BMFRfbkJXbkV6em1LSXB3dVUzNU5ibXBZcmd2NzZBOThGazFzTHh3QnZ0ZHRhQWg3NVlUV3JMVk1sTEp3UHNsSjlHbFdoaFhDMVZhSDZSWG0zdlkzaXFDaEtYTmtFWEU0aEQ3MElRRg?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr"/>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>5a0bffedeb7b446f97d768fed5217d25</t>
+        </is>
+      </c>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>195439b6b4eeeb8fc1a76ca1</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>be86cfe130733a2e1daf4532</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr"/>
+      <c r="AF9" s="4" t="inlineStr"/>
+      <c r="AG9" s="4" t="inlineStr"/>
+      <c r="AH9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr"/>
+      <c r="AL9" s="4" t="inlineStr"/>
+      <c r="AM9" s="4" t="inlineStr"/>
+      <c r="AN9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>'-0.637</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOVFk1TmwtTk5nSGlObGczd2tKb3JxZ19QMHF3TjY0dnpsX3dGVTNxcUViLVhCcmZHZFVSZEFtNzhwUmtPb1Q2bUNGSi1MQmduT3ZDM3FCbmNCMHBMQnBPbnlHZFBxTk5OclJCTm5tZDdVOTdlYUlpTEZFb0REc0Q1NlA3Qmw3V0ludFFqakVJSzlhOUNxbXRRSnhQUFlRcG16SGFUZ0hOcUhQS3Byb3RpbGdoQzJRdXJtYTkxcVVkREx4WldpdG5zOHVRbWVOLXBVak9Va3JMNk1vWXhCSGdLelFrNmMtZ3gxd3dr0gHwAUFVX3lxTE5Bc2F6dVA4TlhXbm01RWRzZkFqM3RTT3pDWFlOOHBLMVA3MG1mNW8xek9sOXFvR09yZnk4VldzU1ZXS052NEV1T18yaXZLUXJzNHo0SzVERHdCdTd4U1VQQ216RHRLcldGZzlQMDhVbTFKeFRfMTdnU3g0UXAtMXNMQllRN0R4VE5BMFRfbkJXbkV6em1LSXB3dVUzNU5ibXBZcmd2NzZBOThGazFzTHh3QnZ0ZHRhQWg3NVlUV3JMVk1sTEp3UHNsSjlHbFdoaFhDMVZhSDZSWG0zdlkzaXFDaEtYTmtFWEU0aEQ3MElRRg?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>195439b6b4eeeb8fc1a76ca1</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>be86cfe130733a2e1daf4532</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr"/>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
+      <c r="AP9" s="4" t="inlineStr"/>
+      <c r="AQ9" s="4" t="inlineStr"/>
+      <c r="AR9" s="4" t="inlineStr"/>
+      <c r="AS9" s="4" t="inlineStr"/>
+      <c r="AT9" s="4" t="inlineStr"/>
+      <c r="AU9" s="4" t="inlineStr"/>
+      <c r="AV9" s="4" t="inlineStr"/>
+      <c r="AW9" s="4" t="inlineStr"/>
+      <c r="AX9" s="4" t="inlineStr"/>
+      <c r="AY9" s="4" t="inlineStr"/>
+      <c r="AZ9" s="4" t="inlineStr"/>
+      <c r="BA9" s="4" t="inlineStr"/>
+      <c r="BB9" s="4" t="inlineStr">
         <is>
           <t>APO</t>
         </is>
       </c>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="BC9" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
+      <c r="BD9" s="4" t="inlineStr"/>
+      <c r="BE9" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF9" s="3" t="inlineStr"/>
-      <c r="BG9" s="3" t="inlineStr">
+      <c r="BF9" s="4" t="inlineStr"/>
+      <c r="BG9" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2223,13 +2383,17 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2274,7 +2438,11 @@
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>98da441165d749408d691aa3ac19af26</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>375626ed67efc8e10dad5c7a</t>
@@ -2295,7 +2463,11 @@
       <c r="AL10" s="3" t="inlineStr"/>
       <c r="AM10" s="3" t="inlineStr"/>
       <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="3" t="inlineStr"/>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr"/>
@@ -2339,341 +2511,401 @@
         </is>
       </c>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>AT&amp;T</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>2026-08-26T01:41:39+08:00</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Elon Musk won't face election bribery charges in Wisconsin, state prosecutor says - ABC News</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>高管不當行為</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>'-0.037</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOQ1RkOWNaYkV0WHVobTRPX0RDbTZLbWFiUGt0eXdCNXkzaGVkNnlKZ3dqeEFkLVpWVnBwcUF5dWpaaVVFM1lwd2s5Ynh0bnJkQkVUcWFuRHQwYUpwUjJPSnRTd3ZRNndnU0dLMnNYYWI3a3M0cTAxdHBYaWdndnJRWTJyM3FtMEtOTGdpNjhKQ1NVNjdFdHJiekxOTjVSUjhkcmU2bk9LVdIBrAFBVV95cUxQdWpwYWtyV0twclNQT244OWlsTDR2X3R1ZXRta1N5ZG16c0xLeFhuX1pJUV9BcTh6aHZ1bGcwMFU4NTE3bEU3R3hsd2JodFk1R21QWDJSV3dPSVJpanRQSm11TnJTNmtneWFVcjVKdFZMeFJLSVllSFhSYmdMMHhOV3ZoOUhQMlV2X2FRV1MtS25PekZ5VFBhTEN1Y0pvOFl2blZDcjhNYkRrYzg3?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>ABC News - Breaking News, Latest News and Videos</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>GOVERNANCE</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>bribery</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>56cebf4f4f1946e4a761a326acf27d63</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>707808060815d6b69eb0ae51</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>72a5f616e77d706c1390a681</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AK11" s="2" t="inlineStr"/>
+      <c r="AL11" s="2" t="inlineStr"/>
+      <c r="AM11" s="2" t="inlineStr"/>
+      <c r="AN11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>'-0.037</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="AP11" s="2" t="inlineStr"/>
+      <c r="AQ11" s="2" t="inlineStr"/>
+      <c r="AR11" s="2" t="inlineStr"/>
+      <c r="AS11" s="2" t="inlineStr"/>
+      <c r="AT11" s="2" t="inlineStr"/>
+      <c r="AU11" s="2" t="inlineStr"/>
+      <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" s="2" t="inlineStr"/>
+      <c r="AX11" s="2" t="inlineStr"/>
+      <c r="AY11" s="2" t="inlineStr"/>
+      <c r="AZ11" s="2" t="inlineStr"/>
+      <c r="BA11" s="2" t="inlineStr"/>
+      <c r="BB11" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="BC11" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOQ1RkOWNaYkV0WHVobTRPX0RDbTZLbWFiUGt0eXdCNXkzaGVkNnlKZ3dqeEFkLVpWVnBwcUF5dWpaaVVFM1lwd2s5Ynh0bnJkQkVUcWFuRHQwYUpwUjJPSnRTd3ZRNndnU0dLMnNYYWI3a3M0cTAxdHBYaWdndnJRWTJyM3FtMEtOTGdpNjhKQ1NVNjdFdHJiekxOTjVSUjhkcmU2bk9LVdIBrAFBVV95cUxQdWpwYWtyV0twclNQT244OWlsTDR2X3R1ZXRta1N5ZG16c0xLeFhuX1pJUV9BcTh6aHZ1bGcwMFU4NTE3bEU3R3hsd2JodFk1R21QWDJSV3dPSVJpanRQSm11TnJTNmtneWFVcjVKdFZMeFJLSVllSFhSYmdMMHhOV3ZoOUhQMlV2X2FRV1MtS25PekZ5VFBhTEN1Y0pvOFl2blZDcjhNYkRrYzg3?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>ABC News - Breaking News, Latest News and Videos</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>GOVERNANCE</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>EXECUTIVE_MISCONDUCT</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>bribery</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>707808060815d6b69eb0ae51</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>72a5f616e77d706c1390a681</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr"/>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
+      <c r="BD11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="BC11" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD11" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BE11" s="3" t="inlineStr">
+      <c r="BE11" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF11" s="3" t="inlineStr">
+      <c r="BF11" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG11" s="3" t="inlineStr"/>
-      <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BG11" s="2" t="inlineStr"/>
+      <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Kroger</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2026-08-26T01:15:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>If you get your meds at Kroger pay attention to this class action lawsuit</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQSUs4dzBEcFFhNWJjNmRuTFVLUHFIbTNVNk1BRTUtVy1LMWllMkt4eXJpYXozQ0V4RXMza2pEWk1jWTNJanVlTVMwWDN4NkdwOTItdFVCdmE2WTZmTzFPZmYyT0tpanpuUk5reVpYcGZtUklUaDNrTFFNbzJoUEliTzRGZVpER3RKREJuaWxYWTlPRmp5NXlzME02c25YbVBDNE1laGhQNXZseXk4VXJUTVp2VUt2MXI2LV84QmhxUDRmYVctNjF4eVdpQ3FveHBDTEdibVE0VC00WFA2ZFFJRHdn?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>11Alive.com</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>8f38917259bd411592167ec4d0abf799</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>3f09a12bd1939d9a08b5e9e1</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>fb90f93be93ce7f3916b3e2b</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>0.008</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQSUs4dzBEcFFhNWJjNmRuTFVLUHFIbTNVNk1BRTUtVy1LMWllMkt4eXJpYXozQ0V4RXMza2pEWk1jWTNJanVlTVMwWDN4NkdwOTItdFVCdmE2WTZmTzFPZmYyT0tpanpuUk5reVpYcGZtUklUaDNrTFFNbzJoUEliTzRGZVpER3RKREJuaWxYWTlPRmp5NXlzME02c25YbVBDNE1laGhQNXZseXk4VXJUTVp2VUt2MXI2LV84QmhxUDRmYVctNjF4eVdpQ3FveHBDTEdibVE0VC00WFA2ZFFJRHdn?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>11Alive.com</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr"/>
-      <c r="AC12" s="3" t="inlineStr">
-        <is>
-          <t>3f09a12bd1939d9a08b5e9e1</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>fb90f93be93ce7f3916b3e2b</t>
-        </is>
-      </c>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr"/>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
+      <c r="AP12" s="2" t="inlineStr"/>
+      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr"/>
+      <c r="AT12" s="2" t="inlineStr"/>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr"/>
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr"/>
+      <c r="AZ12" s="2" t="inlineStr"/>
+      <c r="BA12" s="2" t="inlineStr"/>
+      <c r="BB12" s="2" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="BC12" s="3" t="inlineStr">
+      <c r="BC12" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
+      <c r="BD12" s="2" t="inlineStr"/>
+      <c r="BE12" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF12" s="3" t="inlineStr"/>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BF12" s="2" t="inlineStr"/>
+      <c r="BG12" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH12"/>
+  <autoFilter ref="A1:BL12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2684,7 +2916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2747,6 +2979,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3050,6 +3286,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -3100,13 +3356,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -3151,7 +3411,11 @@
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>e546a631c77e4fa8bc8a4cc27a6724fb</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>fdde003085f4c9c55c521d98</t>
@@ -3172,7 +3436,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -3216,6 +3484,18 @@
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3266,13 +3546,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -3321,7 +3605,11 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>6e6e27fa253d47d58879905fb3efd898</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>64533d28a77ef9a251dd91c9</t>
@@ -3342,7 +3630,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -3386,6 +3678,18 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -3548,6 +3852,10 @@
         </is>
       </c>
       <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr"/>
+      <c r="BL4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3598,13 +3906,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -3649,7 +3961,11 @@
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>43cedf0db261483aa353f50bb7820965</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>5e643003c46200dc2257791e</t>
@@ -3670,7 +3986,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -3714,6 +4034,18 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -3764,13 +4096,17 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
@@ -3819,7 +4155,11 @@
         </is>
       </c>
       <c r="AA6" s="5" t="inlineStr"/>
-      <c r="AB6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr">
+        <is>
+          <t>89b8cdd9449f41fba33e7fcb2fab5ff6</t>
+        </is>
+      </c>
       <c r="AC6" s="5" t="inlineStr">
         <is>
           <t>6f7308482508a9851ede7f08</t>
@@ -3840,7 +4180,11 @@
       <c r="AL6" s="5" t="inlineStr"/>
       <c r="AM6" s="5" t="inlineStr"/>
       <c r="AN6" s="5" t="inlineStr"/>
-      <c r="AO6" s="5" t="inlineStr"/>
+      <c r="AO6" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="5" t="inlineStr"/>
       <c r="AQ6" s="5" t="inlineStr"/>
       <c r="AR6" s="5" t="inlineStr"/>
@@ -3884,168 +4228,208 @@
         </is>
       </c>
       <c r="BH6" s="5" t="inlineStr"/>
+      <c r="BI6" s="5" t="inlineStr"/>
+      <c r="BJ6" s="5" t="inlineStr"/>
+      <c r="BK6" s="5" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>APO</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Apollo Global Management</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>2026-08-26T13:23:59+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>The Bull Case For Apollo Global Management (APO) Could Change Following Cybersecurity Breach And Legal Settlement News - Learn Why</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>資料外洩</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>'-0.637</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOVFk1TmwtTk5nSGlObGczd2tKb3JxZ19QMHF3TjY0dnpsX3dGVTNxcUViLVhCcmZHZFVSZEFtNzhwUmtPb1Q2bUNGSi1MQmduT3ZDM3FCbmNCMHBMQnBPbnlHZFBxTk5OclJCTm5tZDdVOTdlYUlpTEZFb0REc0Q1NlA3Qmw3V0ludFFqakVJSzlhOUNxbXRRSnhQUFlRcG16SGFUZ0hOcUhQS3Byb3RpbGdoQzJRdXJtYTkxcVVkREx4WldpdG5zOHVRbWVOLXBVak9Va3JMNk1vWXhCSGdLelFrNmMtZ3gxd3dr0gHwAUFVX3lxTE5Bc2F6dVA4TlhXbm01RWRzZkFqM3RTT3pDWFlOOHBLMVA3MG1mNW8xek9sOXFvR09yZnk4VldzU1ZXS052NEV1T18yaXZLUXJzNHo0SzVERHdCdTd4U1VQQ216RHRLcldGZzlQMDhVbTFKeFRfMTdnU3g0UXAtMXNMQllRN0R4VE5BMFRfbkJXbkV6em1LSXB3dVUzNU5ibXBZcmd2NzZBOThGazFzTHh3QnZ0ZHRhQWg3NVlUV3JMVk1sTEp3UHNsSjlHbFdoaFhDMVZhSDZSWG0zdlkzaXFDaEtYTmtFWEU0aEQ3MElRRg?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>5a0bffedeb7b446f97d768fed5217d25</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>195439b6b4eeeb8fc1a76ca1</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>be86cfe130733a2e1daf4532</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr"/>
+      <c r="AF7" s="4" t="inlineStr"/>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
+      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>'-0.637</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOVFk1TmwtTk5nSGlObGczd2tKb3JxZ19QMHF3TjY0dnpsX3dGVTNxcUViLVhCcmZHZFVSZEFtNzhwUmtPb1Q2bUNGSi1MQmduT3ZDM3FCbmNCMHBMQnBPbnlHZFBxTk5OclJCTm5tZDdVOTdlYUlpTEZFb0REc0Q1NlA3Qmw3V0ludFFqakVJSzlhOUNxbXRRSnhQUFlRcG16SGFUZ0hOcUhQS3Byb3RpbGdoQzJRdXJtYTkxcVVkREx4WldpdG5zOHVRbWVOLXBVak9Va3JMNk1vWXhCSGdLelFrNmMtZ3gxd3dr0gHwAUFVX3lxTE5Bc2F6dVA4TlhXbm01RWRzZkFqM3RTT3pDWFlOOHBLMVA3MG1mNW8xek9sOXFvR09yZnk4VldzU1ZXS052NEV1T18yaXZLUXJzNHo0SzVERHdCdTd4U1VQQ216RHRLcldGZzlQMDhVbTFKeFRfMTdnU3g0UXAtMXNMQllRN0R4VE5BMFRfbkJXbkV6em1LSXB3dVUzNU5ibXBZcmd2NzZBOThGazFzTHh3QnZ0ZHRhQWg3NVlUV3JMVk1sTEp3UHNsSjlHbFdoaFhDMVZhSDZSWG0zdlkzaXFDaEtYTmtFWEU0aEQ3MElRRg?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>195439b6b4eeeb8fc1a76ca1</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>be86cfe130733a2e1daf4532</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr"/>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AS7" s="4" t="inlineStr"/>
+      <c r="AT7" s="4" t="inlineStr"/>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr"/>
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr">
         <is>
           <t>APO</t>
         </is>
       </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="BC7" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF7" s="3" t="inlineStr"/>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BF7" s="4" t="inlineStr"/>
+      <c r="BG7" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -4096,13 +4480,17 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -4147,7 +4535,11 @@
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>98da441165d749408d691aa3ac19af26</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
           <t>375626ed67efc8e10dad5c7a</t>
@@ -4168,7 +4560,11 @@
       <c r="AL8" s="3" t="inlineStr"/>
       <c r="AM8" s="3" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="3" t="inlineStr"/>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr"/>
@@ -4212,341 +4608,21 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26T01:41:39+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Elon Musk won't face election bribery charges in Wisconsin, state prosecutor says - ABC News</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>高管不當行為</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>'-0.037</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOQ1RkOWNaYkV0WHVobTRPX0RDbTZLbWFiUGt0eXdCNXkzaGVkNnlKZ3dqeEFkLVpWVnBwcUF5dWpaaVVFM1lwd2s5Ynh0bnJkQkVUcWFuRHQwYUpwUjJPSnRTd3ZRNndnU0dLMnNYYWI3a3M0cTAxdHBYaWdndnJRWTJyM3FtMEtOTGdpNjhKQ1NVNjdFdHJiekxOTjVSUjhkcmU2bk9LVdIBrAFBVV95cUxQdWpwYWtyV0twclNQT244OWlsTDR2X3R1ZXRta1N5ZG16c0xLeFhuX1pJUV9BcTh6aHZ1bGcwMFU4NTE3bEU3R3hsd2JodFk1R21QWDJSV3dPSVJpanRQSm11TnJTNmtneWFVcjVKdFZMeFJLSVllSFhSYmdMMHhOV3ZoOUhQMlV2X2FRV1MtS25PekZ5VFBhTEN1Y0pvOFl2blZDcjhNYkRrYzg3?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>ABC News - Breaking News, Latest News and Videos</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>GOVERNANCE</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>EXECUTIVE_MISCONDUCT</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>bribery</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>707808060815d6b69eb0ae51</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>72a5f616e77d706c1390a681</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr"/>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BC9" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD9" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BE9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="3" t="inlineStr"/>
-      <c r="BH9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Kroger</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26T01:15:00+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>If you get your meds at Kroger pay attention to this class action lawsuit</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>0.008</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQSUs4dzBEcFFhNWJjNmRuTFVLUHFIbTNVNk1BRTUtVy1LMWllMkt4eXJpYXozQ0V4RXMza2pEWk1jWTNJanVlTVMwWDN4NkdwOTItdFVCdmE2WTZmTzFPZmYyT0tpanpuUk5reVpYcGZtUklUaDNrTFFNbzJoUEliTzRGZVpER3RKREJuaWxYWTlPRmp5NXlzME02c25YbVBDNE1laGhQNXZseXk4VXJUTVp2VUt2MXI2LV84QmhxUDRmYVctNjF4eVdpQ3FveHBDTEdibVE0VC00WFA2ZFFJRHdn?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>11Alive.com</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr">
-        <is>
-          <t>3f09a12bd1939d9a08b5e9e1</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>fb90f93be93ce7f3916b3e2b</t>
-        </is>
-      </c>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr"/>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="BC10" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD10" s="3" t="inlineStr"/>
-      <c r="BE10" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF10" s="3" t="inlineStr"/>
-      <c r="BG10" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH10"/>
+  <autoFilter ref="A1:BL8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4557,7 +4633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH2"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4620,6 +4696,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4923,179 +5003,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26T01:41:39+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Elon Musk won't face election bribery charges in Wisconsin, state prosecutor says - ABC News</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>高管不當行為</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>'-0.037</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOQ1RkOWNaYkV0WHVobTRPX0RDbTZLbWFiUGt0eXdCNXkzaGVkNnlKZ3dqeEFkLVpWVnBwcUF5dWpaaVVFM1lwd2s5Ynh0bnJkQkVUcWFuRHQwYUpwUjJPSnRTd3ZRNndnU0dLMnNYYWI3a3M0cTAxdHBYaWdndnJRWTJyM3FtMEtOTGdpNjhKQ1NVNjdFdHJiekxOTjVSUjhkcmU2bk9LVdIBrAFBVV95cUxQdWpwYWtyV0twclNQT244OWlsTDR2X3R1ZXRta1N5ZG16c0xLeFhuX1pJUV9BcTh6aHZ1bGcwMFU4NTE3bEU3R3hsd2JodFk1R21QWDJSV3dPSVJpanRQSm11TnJTNmtneWFVcjVKdFZMeFJLSVllSFhSYmdMMHhOV3ZoOUhQMlV2X2FRV1MtS25PekZ5VFBhTEN1Y0pvOFl2blZDcjhNYkRrYzg3?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>ABC News - Breaking News, Latest News and Videos</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>GOVERNANCE</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>EXECUTIVE_MISCONDUCT</t>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>bribery</t>
-        </is>
-      </c>
-      <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
-      <c r="AC2" s="3" t="inlineStr">
-        <is>
-          <t>707808060815d6b69eb0ae51</t>
-        </is>
-      </c>
-      <c r="AD2" s="3" t="inlineStr">
-        <is>
-          <t>72a5f616e77d706c1390a681</t>
-        </is>
-      </c>
-      <c r="AE2" s="3" t="inlineStr"/>
-      <c r="AF2" s="3" t="inlineStr"/>
-      <c r="AG2" s="3" t="inlineStr"/>
-      <c r="AH2" s="3" t="inlineStr"/>
-      <c r="AI2" s="3" t="inlineStr"/>
-      <c r="AJ2" s="3" t="inlineStr"/>
-      <c r="AK2" s="3" t="inlineStr"/>
-      <c r="AL2" s="3" t="inlineStr"/>
-      <c r="AM2" s="3" t="inlineStr"/>
-      <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="3" t="inlineStr"/>
-      <c r="AQ2" s="3" t="inlineStr"/>
-      <c r="AR2" s="3" t="inlineStr"/>
-      <c r="AS2" s="3" t="inlineStr"/>
-      <c r="AT2" s="3" t="inlineStr"/>
-      <c r="AU2" s="3" t="inlineStr"/>
-      <c r="AV2" s="3" t="inlineStr"/>
-      <c r="AW2" s="3" t="inlineStr"/>
-      <c r="AX2" s="3" t="inlineStr"/>
-      <c r="AY2" s="3" t="inlineStr"/>
-      <c r="AZ2" s="3" t="inlineStr"/>
-      <c r="BA2" s="3" t="inlineStr"/>
-      <c r="BB2" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BC2" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BE2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="3" t="inlineStr"/>
-      <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH2"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5106,7 +5036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5169,6 +5099,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5472,9 +5406,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5485,7 +5439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5535,134 +5489,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5672,46 +5626,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5720,12 +5708,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5735,90 +5723,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5828,94 +5820,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5923,89 +5915,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-08-26.xlsx
+++ b/news_daily/2026-08-26.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
+        <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
+        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -1421,170 +1421,194 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>EME</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Emcor</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-08-26T21:24:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Can EMCOR's Mechanical Construction Growth Offset Margin Pressure?</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0.847</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNTnJnYU1aTmRoc1lDUnp3WG0yVTJBZXdBYkoxeG5mWFZVUGRFYTEtYlp6SmR3cEJuUElkdG41N0xwYkQ5Ym9ZZHE2SHJVal9Fc2NxRWZEMmpfMVRtc0c3WUh2bzhJcG54Q3M2ODNqUDVVSjNCc1V5NzM2WTBSc1kwWkZBOFREYUk0SzFUcXNvdXFnRm9OU185UzJfcUoxUUlNZVFRSmplVFI5cDdXeHc?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>b56b90e63a374bcb8d9554b5911043fd</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>916fc3310745007567e1f27d</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>5d78fbb6f4e63672fc45fc0c</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>0.847</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNTnJnYU1aTmRoc1lDUnp3WG0yVTJBZXdBYkoxeG5mWFZVUGRFYTEtYlp6SmR3cEJuUElkdG41N0xwYkQ5Ym9ZZHE2SHJVal9Fc2NxRWZEMmpfMVRtc0c3WUh2bzhJcG54Q3M2ODNqUDVVSjNCc1V5NzM2WTBSc1kwWkZBOFREYUk0SzFUcXNvdXFnRm9OU185UzJfcUoxUUlNZVFRSmplVFI5cDdXeHc?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>916fc3310745007567e1f27d</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>5d78fbb6f4e63672fc45fc0c</t>
-        </is>
-      </c>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr"/>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr"/>
+      <c r="AX5" s="2" t="inlineStr"/>
+      <c r="AY5" s="2" t="inlineStr"/>
+      <c r="AZ5" s="2" t="inlineStr"/>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr">
         <is>
           <t>EME</t>
         </is>
       </c>
-      <c r="BC5" s="4" t="inlineStr">
+      <c r="BC5" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="4" t="inlineStr"/>
-      <c r="BE5" s="4" t="inlineStr">
+      <c r="BD5" s="2" t="inlineStr"/>
+      <c r="BE5" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF5" s="4" t="inlineStr"/>
-      <c r="BG5" s="4" t="inlineStr">
+      <c r="BF5" s="2" t="inlineStr"/>
+      <c r="BG5" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH5" s="4" t="inlineStr"/>
-      <c r="BI5" s="4" t="inlineStr"/>
-      <c r="BJ5" s="4" t="inlineStr"/>
-      <c r="BK5" s="4" t="inlineStr"/>
-      <c r="BL5" s="4" t="inlineStr"/>
+      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1951,384 +1975,384 @@
       <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>ECHO</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>EchoStar Corporation</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>2026-08-26T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>US Bankruptcy: Hughes Satellite Systems judge to order examiner appointment to investigate dealings with parent EchoStar; scope of probe subject to further hearing</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>破產</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>'-0.268</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
-      <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U8" s="5" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiqAJBVV95cUxPMUg4MFFKSTkxQm5zVEx2cDBMU2U2TGhnQVpfRXA5c1M3dWZ4UlVrN2I4dW5kNTQxdTR3LTd5MFR4bEppd3JpN21ud1dESTJGZFRwajdWTHRwa3dZQkM1cmNRTUZfRWx6RWQ2c1NqN2VydElISVZzQS02QmtTUjJTWS0yWEFuRHB6Y2pjVFdzVFQwcEFnMEt5czQ0THNKbEdVUUdrOEFzS3l3ZHl5X3V2dDhWMkZPbV81Zm4teGpnbnN2dmlSeTNIRlR4Z25FNlZURDRmSXF3R0hCY3kwODc2RmRiN0hIdUFuXzZQaVd2YUNiUmVNWXhsajNrUkpGX1RoQ0Nja2xNY0RHSEtTREQ0cFA3WXp5NXJub2tYcDFXeTBlSVBwN25sYw?oc=5</t>
         </is>
       </c>
-      <c r="V8" s="5" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>know.creditsights.com</t>
         </is>
       </c>
-      <c r="W8" s="5" t="inlineStr"/>
-      <c r="X8" s="5" t="inlineStr">
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr">
         <is>
           <t>FINANCIAL</t>
         </is>
       </c>
-      <c r="Y8" s="5" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>BANKRUPTCY</t>
         </is>
       </c>
-      <c r="Z8" s="5" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>bankruptcy</t>
         </is>
       </c>
-      <c r="AA8" s="5" t="inlineStr"/>
-      <c r="AB8" s="5" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr">
         <is>
           <t>89b8cdd9449f41fba33e7fcb2fab5ff6</t>
         </is>
       </c>
-      <c r="AC8" s="5" t="inlineStr">
+      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>6f7308482508a9851ede7f08</t>
         </is>
       </c>
-      <c r="AD8" s="5" t="inlineStr">
+      <c r="AD8" s="4" t="inlineStr">
         <is>
           <t>5702810c2ddce843eef3cf9d</t>
         </is>
       </c>
-      <c r="AE8" s="5" t="inlineStr"/>
-      <c r="AF8" s="5" t="inlineStr"/>
-      <c r="AG8" s="5" t="inlineStr"/>
-      <c r="AH8" s="5" t="inlineStr"/>
-      <c r="AI8" s="5" t="inlineStr"/>
-      <c r="AJ8" s="5" t="inlineStr"/>
-      <c r="AK8" s="5" t="inlineStr"/>
-      <c r="AL8" s="5" t="inlineStr"/>
-      <c r="AM8" s="5" t="inlineStr"/>
-      <c r="AN8" s="5" t="inlineStr"/>
-      <c r="AO8" s="5" t="inlineStr">
+      <c r="AE8" s="4" t="inlineStr"/>
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP8" s="5" t="inlineStr"/>
-      <c r="AQ8" s="5" t="inlineStr"/>
-      <c r="AR8" s="5" t="inlineStr"/>
-      <c r="AS8" s="5" t="inlineStr"/>
-      <c r="AT8" s="5" t="inlineStr"/>
-      <c r="AU8" s="5" t="inlineStr"/>
-      <c r="AV8" s="5" t="inlineStr"/>
-      <c r="AW8" s="5" t="inlineStr">
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX8" s="5" t="inlineStr"/>
-      <c r="AY8" s="5" t="inlineStr"/>
-      <c r="AZ8" s="5" t="inlineStr"/>
-      <c r="BA8" s="5" t="inlineStr"/>
-      <c r="BB8" s="5" t="inlineStr">
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr">
         <is>
           <t>ECHO</t>
         </is>
       </c>
-      <c r="BC8" s="5" t="inlineStr">
+      <c r="BC8" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="5" t="inlineStr"/>
-      <c r="BE8" s="5" t="inlineStr">
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF8" s="5" t="inlineStr">
+      <c r="BF8" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="5" t="inlineStr">
+      <c r="BG8" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH8" s="5" t="inlineStr"/>
-      <c r="BI8" s="5" t="inlineStr"/>
-      <c r="BJ8" s="5" t="inlineStr"/>
-      <c r="BK8" s="5" t="inlineStr">
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL8" s="5" t="inlineStr">
+      <c r="BL8" s="4" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>APO</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Apollo Global Management</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026-08-26T13:23:59+08:00</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>The Bull Case For Apollo Global Management (APO) Could Change Following Cybersecurity Breach And Legal Settlement News - Learn Why</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>資料外洩</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>'-0.637</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U9" s="4" t="inlineStr">
+      <c r="U9" s="5" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOVFk1TmwtTk5nSGlObGczd2tKb3JxZ19QMHF3TjY0dnpsX3dGVTNxcUViLVhCcmZHZFVSZEFtNzhwUmtPb1Q2bUNGSi1MQmduT3ZDM3FCbmNCMHBMQnBPbnlHZFBxTk5OclJCTm5tZDdVOTdlYUlpTEZFb0REc0Q1NlA3Qmw3V0ludFFqakVJSzlhOUNxbXRRSnhQUFlRcG16SGFUZ0hOcUhQS3Byb3RpbGdoQzJRdXJtYTkxcVVkREx4WldpdG5zOHVRbWVOLXBVak9Va3JMNk1vWXhCSGdLelFrNmMtZ3gxd3dr0gHwAUFVX3lxTE5Bc2F6dVA4TlhXbm01RWRzZkFqM3RTT3pDWFlOOHBLMVA3MG1mNW8xek9sOXFvR09yZnk4VldzU1ZXS052NEV1T18yaXZLUXJzNHo0SzVERHdCdTd4U1VQQ216RHRLcldGZzlQMDhVbTFKeFRfMTdnU3g0UXAtMXNMQllRN0R4VE5BMFRfbkJXbkV6em1LSXB3dVUzNU5ibXBZcmd2NzZBOThGazFzTHh3QnZ0ZHRhQWg3NVlUV3JMVk1sTEp3UHNsSjlHbFdoaFhDMVZhSDZSWG0zdlkzaXFDaEtYTmtFWEU0aEQ3MElRRg?oc=5</t>
         </is>
       </c>
-      <c r="V9" s="4" t="inlineStr">
+      <c r="V9" s="5" t="inlineStr">
         <is>
           <t>simplywall.st</t>
         </is>
       </c>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr">
+      <c r="W9" s="5" t="inlineStr"/>
+      <c r="X9" s="5" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y9" s="4" t="inlineStr">
+      <c r="Y9" s="5" t="inlineStr">
         <is>
           <t>DATA_BREACH</t>
         </is>
       </c>
-      <c r="Z9" s="4" t="inlineStr">
+      <c r="Z9" s="5" t="inlineStr">
         <is>
           <t>settlement</t>
         </is>
       </c>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr">
+      <c r="AA9" s="5" t="inlineStr"/>
+      <c r="AB9" s="5" t="inlineStr">
         <is>
           <t>5a0bffedeb7b446f97d768fed5217d25</t>
         </is>
       </c>
-      <c r="AC9" s="4" t="inlineStr">
+      <c r="AC9" s="5" t="inlineStr">
         <is>
           <t>195439b6b4eeeb8fc1a76ca1</t>
         </is>
       </c>
-      <c r="AD9" s="4" t="inlineStr">
+      <c r="AD9" s="5" t="inlineStr">
         <is>
           <t>be86cfe130733a2e1daf4532</t>
         </is>
       </c>
-      <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="4" t="inlineStr"/>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr">
+      <c r="AE9" s="5" t="inlineStr"/>
+      <c r="AF9" s="5" t="inlineStr"/>
+      <c r="AG9" s="5" t="inlineStr"/>
+      <c r="AH9" s="5" t="inlineStr"/>
+      <c r="AI9" s="5" t="inlineStr"/>
+      <c r="AJ9" s="5" t="inlineStr"/>
+      <c r="AK9" s="5" t="inlineStr"/>
+      <c r="AL9" s="5" t="inlineStr"/>
+      <c r="AM9" s="5" t="inlineStr"/>
+      <c r="AN9" s="5" t="inlineStr"/>
+      <c r="AO9" s="5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP9" s="4" t="inlineStr"/>
-      <c r="AQ9" s="4" t="inlineStr"/>
-      <c r="AR9" s="4" t="inlineStr"/>
-      <c r="AS9" s="4" t="inlineStr"/>
-      <c r="AT9" s="4" t="inlineStr"/>
-      <c r="AU9" s="4" t="inlineStr"/>
-      <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="inlineStr"/>
-      <c r="AX9" s="4" t="inlineStr"/>
-      <c r="AY9" s="4" t="inlineStr"/>
-      <c r="AZ9" s="4" t="inlineStr"/>
-      <c r="BA9" s="4" t="inlineStr"/>
-      <c r="BB9" s="4" t="inlineStr">
+      <c r="AP9" s="5" t="inlineStr"/>
+      <c r="AQ9" s="5" t="inlineStr"/>
+      <c r="AR9" s="5" t="inlineStr"/>
+      <c r="AS9" s="5" t="inlineStr"/>
+      <c r="AT9" s="5" t="inlineStr"/>
+      <c r="AU9" s="5" t="inlineStr"/>
+      <c r="AV9" s="5" t="inlineStr"/>
+      <c r="AW9" s="5" t="inlineStr"/>
+      <c r="AX9" s="5" t="inlineStr"/>
+      <c r="AY9" s="5" t="inlineStr"/>
+      <c r="AZ9" s="5" t="inlineStr"/>
+      <c r="BA9" s="5" t="inlineStr"/>
+      <c r="BB9" s="5" t="inlineStr">
         <is>
           <t>APO</t>
         </is>
       </c>
-      <c r="BC9" s="4" t="inlineStr">
+      <c r="BC9" s="5" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="4" t="inlineStr"/>
-      <c r="BE9" s="4" t="inlineStr">
+      <c r="BD9" s="5" t="inlineStr"/>
+      <c r="BE9" s="5" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF9" s="4" t="inlineStr"/>
-      <c r="BG9" s="4" t="inlineStr">
+      <c r="BF9" s="5" t="inlineStr"/>
+      <c r="BG9" s="5" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH9" s="4" t="inlineStr"/>
-      <c r="BI9" s="4" t="inlineStr">
+      <c r="BH9" s="5" t="inlineStr"/>
+      <c r="BI9" s="5" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ9" s="4" t="inlineStr"/>
-      <c r="BK9" s="4" t="inlineStr">
+      <c r="BJ9" s="5" t="inlineStr"/>
+      <c r="BK9" s="5" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL9" s="4" t="inlineStr">
+      <c r="BL9" s="5" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
@@ -2916,7 +2940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL8"/>
+  <dimension ref="A1:BL7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3692,356 +3716,384 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>EME</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Emcor</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-26T21:24:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Can EMCOR's Mechanical Construction Growth Offset Margin Pressure?</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26T21:00:40+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>消息稱Meta就各州指控其平台危害兒童健康的訴訟達成和解</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2634384</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>訴訟</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>43cedf0db261483aa353f50bb7820965</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>5e643003c46200dc2257791e</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>99f71492bbe380c4ae85903d</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>0.847</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNTnJnYU1aTmRoc1lDUnp3WG0yVTJBZXdBYkoxeG5mWFZVUGRFYTEtYlp6SmR3cEJuUElkdG41N0xwYkQ5Ym9ZZHE2SHJVal9Fc2NxRWZEMmpfMVRtc0c3WUh2bzhJcG54Q3M2ODNqUDVVSjNCc1V5NzM2WTBSc1kwWkZBOFREYUk0SzFUcXNvdXFnRm9OU185UzJfcUoxUUlNZVFRSmplVFI5cDdXeHc?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>916fc3310745007567e1f27d</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>5d78fbb6f4e63672fc45fc0c</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr"/>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>EME</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="BC4" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr"/>
-      <c r="BG4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH4" s="4" t="inlineStr"/>
-      <c r="BI4" s="4" t="inlineStr"/>
-      <c r="BJ4" s="4" t="inlineStr"/>
-      <c r="BK4" s="4" t="inlineStr"/>
-      <c r="BL4" s="4" t="inlineStr"/>
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+        </is>
+      </c>
+      <c r="BF4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="BG4" s="3" t="inlineStr">
+        <is>
+          <t>上市公司</t>
+        </is>
+      </c>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26T21:00:40+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>消息稱Meta就各州指控其平台危害兒童健康的訴訟達成和解</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>ECHO</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>EchoStar Corporation</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26T15:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>US Bankruptcy: Hughes Satellite Systems judge to order examiner appointment to investigate dealings with parent EchoStar; scope of probe subject to further hearing</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>破產</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>'-0.268</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2634384</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr">
-        <is>
-          <t>43cedf0db261483aa353f50bb7820965</t>
-        </is>
-      </c>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>5e643003c46200dc2257791e</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>99f71492bbe380c4ae85903d</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAJBVV95cUxPMUg4MFFKSTkxQm5zVEx2cDBMU2U2TGhnQVpfRXA5c1M3dWZ4UlVrN2I4dW5kNTQxdTR3LTd5MFR4bEppd3JpN21ud1dESTJGZFRwajdWTHRwa3dZQkM1cmNRTUZfRWx6RWQ2c1NqN2VydElISVZzQS02QmtTUjJTWS0yWEFuRHB6Y2pjVFdzVFQwcEFnMEt5czQ0THNKbEdVUUdrOEFzS3l3ZHl5X3V2dDhWMkZPbV81Zm4teGpnbnN2dmlSeTNIRlR4Z25FNlZURDRmSXF3R0hCY3kwODc2RmRiN0hIdUFuXzZQaVd2YUNiUmVNWXhsajNrUkpGX1RoQ0Nja2xNY0RHSEtTREQ0cFA3WXp5NXJub2tYcDFXeTBlSVBwN25sYw?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>know.creditsights.com</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>BANKRUPTCY</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>bankruptcy</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>89b8cdd9449f41fba33e7fcb2fab5ff6</t>
+        </is>
+      </c>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>6f7308482508a9851ede7f08</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>5702810c2ddce843eef3cf9d</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr"/>
+      <c r="AF5" s="4" t="inlineStr"/>
+      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
+      <c r="AL5" s="4" t="inlineStr"/>
+      <c r="AM5" s="4" t="inlineStr"/>
+      <c r="AN5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
+      <c r="AP5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AR5" s="4" t="inlineStr"/>
+      <c r="AS5" s="4" t="inlineStr"/>
+      <c r="AT5" s="4" t="inlineStr"/>
+      <c r="AU5" s="4" t="inlineStr"/>
+      <c r="AV5" s="4" t="inlineStr"/>
+      <c r="AW5" s="4" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="BC5" s="3" t="inlineStr">
+      <c r="AX5" s="4" t="inlineStr"/>
+      <c r="AY5" s="4" t="inlineStr"/>
+      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="inlineStr">
+        <is>
+          <t>ECHO</t>
+        </is>
+      </c>
+      <c r="BC5" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
-        <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG5" s="3" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH5" s="3" t="inlineStr"/>
-      <c r="BI5" s="3" t="inlineStr"/>
-      <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr">
+      <c r="BD5" s="4" t="inlineStr"/>
+      <c r="BE5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG5" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL5" s="3" t="inlineStr">
+      <c r="BL5" s="4" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
@@ -4060,38 +4112,38 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>ECHO</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>EchoStar Corporation</t>
+          <t>Apollo Global Management</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T15:00:00+08:00</t>
+          <t>2026-08-26T13:23:59+08:00</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>US Bankruptcy: Hughes Satellite Systems judge to order examiner appointment to investigate dealings with parent EchoStar; scope of probe subject to further hearing</t>
+          <t>The Bull Case For Apollo Global Management (APO) Could Change Following Cybersecurity Breach And Legal Settlement News - Learn Why</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>破產</t>
+          <t>資料外洩</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -4116,7 +4168,7 @@
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>'-0.268</t>
+          <t>'-0.637</t>
         </is>
       </c>
       <c r="P6" s="5" t="inlineStr"/>
@@ -4130,44 +4182,44 @@
       </c>
       <c r="U6" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAJBVV95cUxPMUg4MFFKSTkxQm5zVEx2cDBMU2U2TGhnQVpfRXA5c1M3dWZ4UlVrN2I4dW5kNTQxdTR3LTd5MFR4bEppd3JpN21ud1dESTJGZFRwajdWTHRwa3dZQkM1cmNRTUZfRWx6RWQ2c1NqN2VydElISVZzQS02QmtTUjJTWS0yWEFuRHB6Y2pjVFdzVFQwcEFnMEt5czQ0THNKbEdVUUdrOEFzS3l3ZHl5X3V2dDhWMkZPbV81Zm4teGpnbnN2dmlSeTNIRlR4Z25FNlZURDRmSXF3R0hCY3kwODc2RmRiN0hIdUFuXzZQaVd2YUNiUmVNWXhsajNrUkpGX1RoQ0Nja2xNY0RHSEtTREQ0cFA3WXp5NXJub2tYcDFXeTBlSVBwN25sYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOVFk1TmwtTk5nSGlObGczd2tKb3JxZ19QMHF3TjY0dnpsX3dGVTNxcUViLVhCcmZHZFVSZEFtNzhwUmtPb1Q2bUNGSi1MQmduT3ZDM3FCbmNCMHBMQnBPbnlHZFBxTk5OclJCTm5tZDdVOTdlYUlpTEZFb0REc0Q1NlA3Qmw3V0ludFFqakVJSzlhOUNxbXRRSnhQUFlRcG16SGFUZ0hOcUhQS3Byb3RpbGdoQzJRdXJtYTkxcVVkREx4WldpdG5zOHVRbWVOLXBVak9Va3JMNk1vWXhCSGdLelFrNmMtZ3gxd3dr0gHwAUFVX3lxTE5Bc2F6dVA4TlhXbm01RWRzZkFqM3RTT3pDWFlOOHBLMVA3MG1mNW8xek9sOXFvR09yZnk4VldzU1ZXS052NEV1T18yaXZLUXJzNHo0SzVERHdCdTd4U1VQQ216RHRLcldGZzlQMDhVbTFKeFRfMTdnU3g0UXAtMXNMQllRN0R4VE5BMFRfbkJXbkV6em1LSXB3dVUzNU5ibXBZcmd2NzZBOThGazFzTHh3QnZ0ZHRhQWg3NVlUV3JMVk1sTEp3UHNsSjlHbFdoaFhDMVZhSDZSWG0zdlkzaXFDaEtYTmtFWEU0aEQ3MElRRg?oc=5</t>
         </is>
       </c>
       <c r="V6" s="5" t="inlineStr">
         <is>
-          <t>know.creditsights.com</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="W6" s="5" t="inlineStr"/>
       <c r="X6" s="5" t="inlineStr">
         <is>
-          <t>FINANCIAL</t>
+          <t>LEGAL</t>
         </is>
       </c>
       <c r="Y6" s="5" t="inlineStr">
         <is>
-          <t>BANKRUPTCY</t>
+          <t>DATA_BREACH</t>
         </is>
       </c>
       <c r="Z6" s="5" t="inlineStr">
         <is>
-          <t>bankruptcy</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA6" s="5" t="inlineStr"/>
       <c r="AB6" s="5" t="inlineStr">
         <is>
-          <t>89b8cdd9449f41fba33e7fcb2fab5ff6</t>
+          <t>5a0bffedeb7b446f97d768fed5217d25</t>
         </is>
       </c>
       <c r="AC6" s="5" t="inlineStr">
         <is>
-          <t>6f7308482508a9851ede7f08</t>
+          <t>195439b6b4eeeb8fc1a76ca1</t>
         </is>
       </c>
       <c r="AD6" s="5" t="inlineStr">
         <is>
-          <t>5702810c2ddce843eef3cf9d</t>
+          <t>be86cfe130733a2e1daf4532</t>
         </is>
       </c>
       <c r="AE6" s="5" t="inlineStr"/>
@@ -4192,18 +4244,14 @@
       <c r="AT6" s="5" t="inlineStr"/>
       <c r="AU6" s="5" t="inlineStr"/>
       <c r="AV6" s="5" t="inlineStr"/>
-      <c r="AW6" s="5" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW6" s="5" t="inlineStr"/>
       <c r="AX6" s="5" t="inlineStr"/>
       <c r="AY6" s="5" t="inlineStr"/>
       <c r="AZ6" s="5" t="inlineStr"/>
       <c r="BA6" s="5" t="inlineStr"/>
       <c r="BB6" s="5" t="inlineStr">
         <is>
-          <t>ECHO</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="BC6" s="5" t="inlineStr">
@@ -4214,21 +4262,21 @@
       <c r="BD6" s="5" t="inlineStr"/>
       <c r="BE6" s="5" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF6" s="5" t="inlineStr"/>
       <c r="BG6" s="5" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH6" s="5" t="inlineStr"/>
-      <c r="BI6" s="5" t="inlineStr"/>
+      <c r="BI6" s="5" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ6" s="5" t="inlineStr"/>
       <c r="BK6" s="5" t="inlineStr">
         <is>
@@ -4242,387 +4290,197 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>APO</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Apollo Global Management</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-26T13:23:59+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>The Bull Case For Apollo Global Management (APO) Could Change Following Cybersecurity Breach And Legal Settlement News - Learn Why</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26T09:36:18+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Meta據悉與多州檢察長就天價訴訟討論庭審中和解</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>'-0.637</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOVFk1TmwtTk5nSGlObGczd2tKb3JxZ19QMHF3TjY0dnpsX3dGVTNxcUViLVhCcmZHZFVSZEFtNzhwUmtPb1Q2bUNGSi1MQmduT3ZDM3FCbmNCMHBMQnBPbnlHZFBxTk5OclJCTm5tZDdVOTdlYUlpTEZFb0REc0Q1NlA3Qmw3V0ludFFqakVJSzlhOUNxbXRRSnhQUFlRcG16SGFUZ0hOcUhQS3Byb3RpbGdoQzJRdXJtYTkxcVVkREx4WldpdG5zOHVRbWVOLXBVak9Va3JMNk1vWXhCSGdLelFrNmMtZ3gxd3dr0gHwAUFVX3lxTE5Bc2F6dVA4TlhXbm01RWRzZkFqM3RTT3pDWFlOOHBLMVA3MG1mNW8xek9sOXFvR09yZnk4VldzU1ZXS052NEV1T18yaXZLUXJzNHo0SzVERHdCdTd4U1VQQ216RHRLcldGZzlQMDhVbTFKeFRfMTdnU3g0UXAtMXNMQllRN0R4VE5BMFRfbkJXbkV6em1LSXB3dVUzNU5ibXBZcmd2NzZBOThGazFzTHh3QnZ0ZHRhQWg3NVlUV3JMVk1sTEp3UHNsSjlHbFdoaFhDMVZhSDZSWG0zdlkzaXFDaEtYTmtFWEU0aEQ3MElRRg?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2632842</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z7" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr">
-        <is>
-          <t>5a0bffedeb7b446f97d768fed5217d25</t>
-        </is>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
-        <is>
-          <t>195439b6b4eeeb8fc1a76ca1</t>
-        </is>
-      </c>
-      <c r="AD7" s="4" t="inlineStr">
-        <is>
-          <t>be86cfe130733a2e1daf4532</t>
-        </is>
-      </c>
-      <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr">
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>訴訟</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>98da441165d749408d691aa3ac19af26</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>375626ed67efc8e10dad5c7a</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>46ee5351059c05b03abf5ed1</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr"/>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="4" t="inlineStr"/>
-      <c r="AZ7" s="4" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr">
-        <is>
-          <t>APO</t>
-        </is>
-      </c>
-      <c r="BC7" s="4" t="inlineStr">
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr"/>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
+      <c r="AU7" s="3" t="inlineStr"/>
+      <c r="AV7" s="3" t="inlineStr"/>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr"/>
+      <c r="AY7" s="3" t="inlineStr"/>
+      <c r="AZ7" s="3" t="inlineStr"/>
+      <c r="BA7" s="3" t="inlineStr"/>
+      <c r="BB7" s="3" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="BC7" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="inlineStr"/>
-      <c r="BG7" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH7" s="4" t="inlineStr"/>
-      <c r="BI7" s="4" t="inlineStr">
-        <is>
-          <t>Action|Event_Code|Level|事件中文</t>
-        </is>
-      </c>
-      <c r="BJ7" s="4" t="inlineStr"/>
-      <c r="BK7" s="4" t="inlineStr">
+      <c r="BD7" s="3" t="inlineStr"/>
+      <c r="BE7" s="3" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+        </is>
+      </c>
+      <c r="BF7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="BG7" s="3" t="inlineStr">
+        <is>
+          <t>上市公司</t>
+        </is>
+      </c>
+      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26T09:36:18+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Meta據悉與多州檢察長就天價訴訟討論庭審中和解</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2632842</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr">
-        <is>
-          <t>98da441165d749408d691aa3ac19af26</t>
-        </is>
-      </c>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>375626ed67efc8e10dad5c7a</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>46ee5351059c05b03abf5ed1</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="BC8" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
-        <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG8" s="3" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr"/>
-      <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL8" s="3" t="inlineStr">
+      <c r="BL7" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL8"/>
+  <autoFilter ref="A1:BL7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-08-26.xlsx
+++ b/news_daily/2026-08-26.xlsx
@@ -896,28 +896,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -957,7 +961,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -966,7 +970,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>35c22a1a886d47cab953293348d21c99</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>b68584678df534a26f0e57bb</t>
@@ -987,7 +995,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1031,10 +1043,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1834,28 +1858,32 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1895,7 +1923,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1904,7 +1932,11 @@
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>b780ecef9c424381975a47d51e277a7e</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>55168e1ead6421801789fd49</t>
@@ -1925,7 +1957,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1969,10 +2005,22 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
